--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22774,7 +22774,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27490,7 +27490,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -28936,7 +28936,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2200,7 +2200,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2854,7 +2854,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8859,7 +8859,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11352,7 +11352,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11764,7 +11764,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14257,7 +14257,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14499,7 +14499,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14911,7 +14911,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15153,7 +15153,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15565,7 +15565,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16219,7 +16219,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16461,7 +16461,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -18058,7 +18058,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18300,7 +18300,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18712,7 +18712,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18954,7 +18954,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19608,7 +19608,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -20020,7 +20020,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20262,7 +20262,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20916,7 +20916,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22120,7 +22120,7 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -22362,7 +22362,7 @@
       </c>
       <c r="AJ104" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK104" t="inlineStr">
@@ -22774,7 +22774,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23016,7 +23016,7 @@
       </c>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23670,7 +23670,7 @@
       </c>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -24082,7 +24082,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24324,7 +24324,7 @@
       </c>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -25528,7 +25528,7 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -25770,7 +25770,7 @@
       </c>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -26182,7 +26182,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26424,7 +26424,7 @@
       </c>
       <c r="AJ123" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK123" t="inlineStr">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27078,7 +27078,7 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
@@ -27490,7 +27490,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27732,7 +27732,7 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -27889,16 +27889,16 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q130" t="n">
         <v>0</v>
       </c>
       <c r="R130" t="n">
-        <v>0</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -28051,10 +28051,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O131" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -28936,7 +28936,7 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -29178,7 +29178,7 @@
       </c>
       <c r="AJ136" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK136" t="inlineStr">
@@ -29446,7 +29446,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9377</v>
+        <v>9380</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>131</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>23</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0.4091261092987516</v>
       </c>
@@ -1554,9 +1548,6 @@
       <c r="O6" t="n">
         <v>26</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.4599337147068316</v>
       </c>
@@ -1953,9 +1944,6 @@
       <c r="P8" t="n">
         <v>34</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.00974112965141591</v>
       </c>
@@ -2607,9 +2595,6 @@
       <c r="P11" t="n">
         <v>210</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.06016580078815709</v>
       </c>
@@ -3261,9 +3246,6 @@
       <c r="P14" t="n">
         <v>228</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.06532286942714199</v>
       </c>
@@ -3915,9 +3897,6 @@
       <c r="P17" t="n">
         <v>103</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.02950989276752467</v>
       </c>
@@ -4569,9 +4548,6 @@
       <c r="P20" t="n">
         <v>92</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.02635835082147835</v>
       </c>
@@ -5220,9 +5196,6 @@
       <c r="O23" t="n">
         <v>120</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="S23" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5613,9 +5586,6 @@
       <c r="O25" t="n">
         <v>17</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.3023975590469034</v>
       </c>
@@ -6009,9 +5979,6 @@
       <c r="O27" t="n">
         <v>24</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.4245541981909216</v>
       </c>
@@ -6408,9 +6375,6 @@
       <c r="P29" t="n">
         <v>315</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.09024870118223564</v>
       </c>
@@ -7062,9 +7026,6 @@
       <c r="P32" t="n">
         <v>86</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.02463932794181671</v>
       </c>
@@ -7716,9 +7677,6 @@
       <c r="P35" t="n">
         <v>196</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.05615474740227996</v>
       </c>
@@ -8370,9 +8328,6 @@
       <c r="P38" t="n">
         <v>98</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0.02807737370113998</v>
       </c>
@@ -9021,9 +8976,6 @@
       <c r="O41" t="n">
         <v>129</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="S41" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9414,9 +9366,6 @@
       <c r="O43" t="n">
         <v>36</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.6403713015110895</v>
       </c>
@@ -9810,9 +9759,6 @@
       <c r="O45" t="n">
         <v>31</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.548382505996607</v>
       </c>
@@ -10209,9 +10155,6 @@
       <c r="P47" t="n">
         <v>116</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.03323444234012487</v>
       </c>
@@ -10863,9 +10806,6 @@
       <c r="P50" t="n">
         <v>181</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.05185719020312587</v>
       </c>
@@ -11517,9 +11457,6 @@
       <c r="P53" t="n">
         <v>117</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.03352094615340181</v>
       </c>
@@ -12171,9 +12108,6 @@
       <c r="P56" t="n">
         <v>136</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0.03896451860566364</v>
       </c>
@@ -12822,9 +12756,6 @@
       <c r="O59" t="n">
         <v>138</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13215,9 +13146,6 @@
       <c r="O61" t="n">
         <v>22</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -13611,9 +13539,6 @@
       <c r="O63" t="n">
         <v>22</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.3891746816750113</v>
       </c>
@@ -14010,9 +13935,6 @@
       <c r="P65" t="n">
         <v>129</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.03695899191272507</v>
       </c>
@@ -14664,9 +14586,6 @@
       <c r="P68" t="n">
         <v>134</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.03839151097910976</v>
       </c>
@@ -15318,9 +15237,6 @@
       <c r="P71" t="n">
         <v>128</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.03667248809944813</v>
       </c>
@@ -15972,9 +15888,6 @@
       <c r="P74" t="n">
         <v>4019</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>1.151458825560016</v>
       </c>
@@ -16623,9 +16536,6 @@
       <c r="O77" t="n">
         <v>107</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17016,9 +16926,6 @@
       <c r="O79" t="n">
         <v>32</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.569218934676524</v>
       </c>
@@ -17412,9 +17319,6 @@
       <c r="O81" t="n">
         <v>20</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.3537951651591013</v>
       </c>
@@ -17811,9 +17715,6 @@
       <c r="P83" t="n">
         <v>142</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.04068354148532527</v>
       </c>
@@ -18465,9 +18366,6 @@
       <c r="P86" t="n">
         <v>129</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.03695899191272507</v>
       </c>
@@ -19119,9 +19017,6 @@
       <c r="P89" t="n">
         <v>366</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="R89" t="n">
         <v>0.1048603956593595</v>
       </c>
@@ -19773,9 +19668,6 @@
       <c r="P92" t="n">
         <v>57</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.0163307173567855</v>
       </c>
@@ -20427,9 +20319,6 @@
       <c r="P95" t="n">
         <v>86</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.02463932794181671</v>
       </c>
@@ -21078,9 +20967,6 @@
       <c r="O98" t="n">
         <v>22</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.3913380175901103</v>
       </c>
@@ -21474,9 +21360,6 @@
       <c r="O100" t="n">
         <v>24</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.4245541981909216</v>
       </c>
@@ -21873,9 +21756,6 @@
       <c r="P102" t="n">
         <v>255</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.07305847238561933</v>
       </c>
@@ -22527,9 +22407,6 @@
       <c r="P105" t="n">
         <v>114</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.032661434713571</v>
       </c>
@@ -23181,9 +23058,6 @@
       <c r="P108" t="n">
         <v>158</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.04526760249775628</v>
       </c>
@@ -23835,9 +23709,6 @@
       <c r="P111" t="n">
         <v>111</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.03180192327374018</v>
       </c>
@@ -24486,9 +24357,6 @@
       <c r="O114" t="n">
         <v>21</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.3735499258814688</v>
       </c>
@@ -24882,9 +24750,6 @@
       <c r="O116" t="n">
         <v>6</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.1061385495477304</v>
       </c>
@@ -25281,9 +25146,6 @@
       <c r="P118" t="n">
         <v>63</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.01804974023644713</v>
       </c>
@@ -25935,9 +25797,6 @@
       <c r="P121" t="n">
         <v>119</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.03409395377995569</v>
       </c>
@@ -26589,9 +26448,6 @@
       <c r="P124" t="n">
         <v>227</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.06503636561386504</v>
       </c>
@@ -27243,9 +27099,6 @@
       <c r="P127" t="n">
         <v>125</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.03581297665961732</v>
       </c>
@@ -27894,9 +27747,6 @@
       <c r="O130" t="n">
         <v>3</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -28285,16 +28135,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R132" t="n">
-        <v>0</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28447,10 +28294,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O133" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -28689,9 +28536,6 @@
       <c r="P134" t="n">
         <v>152</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.04354857961809466</v>
       </c>
@@ -29263,6 +29107,657 @@
         </is>
       </c>
       <c r="BC136" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N137" t="n">
+        <v>108</v>
+      </c>
+      <c r="O137" t="n">
+        <v>108</v>
+      </c>
+      <c r="P137" t="n">
+        <v>108</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.03094241183390936</v>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO137" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP137" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ137" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR137" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS137" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT137" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU137" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV137" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA137" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB137" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC137" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N138" t="n">
+        <v>108</v>
+      </c>
+      <c r="O138" t="n">
+        <v>108</v>
+      </c>
+      <c r="P138" t="n">
+        <v>108</v>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD138" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE138" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF138" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG138" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH138" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM138" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN138" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO138" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP138" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ138" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR138" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS138" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT138" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU138" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV138" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA138" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB138" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC138" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N139" t="n">
+        <v>203</v>
+      </c>
+      <c r="O139" t="n">
+        <v>203</v>
+      </c>
+      <c r="P139" t="n">
+        <v>203</v>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD139" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE139" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF139" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG139" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH139" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI139" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM139" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO139" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP139" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ139" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR139" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS139" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT139" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU139" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV139" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA139" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB139" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC139" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29301,7 +29796,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-08</t>
         </is>
       </c>
     </row>
@@ -29384,7 +29879,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -29394,7 +29889,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -29414,7 +29909,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -29446,7 +29941,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9380</v>
+        <v>9491</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -27742,13 +27742,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O130" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R130" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -27901,10 +27901,10 @@
         </is>
       </c>
       <c r="N131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O131" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
@@ -29941,7 +29941,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9491</v>
+        <v>9493</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O2" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -916,10 +916,10 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O3" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -5191,10 +5191,10 @@
         </is>
       </c>
       <c r="N23" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O23" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -5347,10 +5347,10 @@
         </is>
       </c>
       <c r="N24" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O24" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="U24" t="inlineStr">
         <is>
@@ -8971,10 +8971,10 @@
         </is>
       </c>
       <c r="N41" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O41" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -9127,10 +9127,10 @@
         </is>
       </c>
       <c r="N42" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O42" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U42" t="inlineStr">
         <is>
@@ -16531,10 +16531,10 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O77" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -16687,10 +16687,10 @@
         </is>
       </c>
       <c r="N78" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O78" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="U78" t="inlineStr">
         <is>
@@ -20923,12 +20923,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -20962,22 +20962,19 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="O98" t="n">
-        <v>22</v>
-      </c>
-      <c r="R98" t="n">
-        <v>0.3913380175901103</v>
+        <v>95</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -20997,12 +20994,12 @@
       </c>
       <c r="AQ98" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS98" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT98" t="n">
@@ -21010,47 +21007,47 @@
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21082,12 +21079,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -21121,24 +21118,24 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="O99" t="n">
-        <v>22</v>
+        <v>95</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="V99" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="W99" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X99" t="inlineStr">
@@ -21153,7 +21150,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -21168,7 +21165,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD99" t="inlineStr">
@@ -21203,17 +21200,17 @@
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>PHO IDTO current-year monthly preliminary chronic hepatitis B notifications captured under the iPHIS carrier classification. Acute and chronic hepatitis B counts are not mutually exclusive when a case progresses to chronic infection.</t>
         </is>
       </c>
       <c r="AM99" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN99" t="b">
@@ -21231,12 +21228,12 @@
       </c>
       <c r="AQ99" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS99" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_CA_ON_PHO_IDTO_CHRONIC_HEPATITIS_B_MONTHLY</t>
         </is>
       </c>
       <c r="AT99" t="n">
@@ -21244,47 +21241,47 @@
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -21316,12 +21313,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -21355,13 +21352,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O100" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R100" t="n">
-        <v>0.4245541981909216</v>
+        <v>0.3913380175901103</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -21370,7 +21367,7 @@
       </c>
       <c r="U100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -21390,12 +21387,12 @@
       </c>
       <c r="AQ100" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS100" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT100" t="n">
@@ -21403,47 +21400,47 @@
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21475,12 +21472,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -21514,29 +21511,29 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="O101" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X101" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
@@ -21561,7 +21558,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD101" t="inlineStr">
@@ -21596,17 +21593,17 @@
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -21624,12 +21621,12 @@
       </c>
       <c r="AQ101" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS101" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT101" t="n">
@@ -21637,47 +21634,47 @@
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -21709,12 +21706,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -21739,7 +21736,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -21748,16 +21745,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="O102" t="n">
-        <v>255</v>
-      </c>
-      <c r="P102" t="n">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="R102" t="n">
-        <v>0.07305847238561933</v>
+        <v>0.4245541981909216</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -21766,12 +21760,12 @@
       </c>
       <c r="U102" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO102" t="inlineStr">
@@ -21781,7 +21775,7 @@
       </c>
       <c r="AP102" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ102" t="inlineStr">
@@ -21789,62 +21783,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR102" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS102" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT102" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU102" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV102" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA102" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB102" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC102" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -21876,12 +21865,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -21906,7 +21895,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
@@ -21915,32 +21904,29 @@
         </is>
       </c>
       <c r="N103" t="n">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="O103" t="n">
-        <v>255</v>
-      </c>
-      <c r="P103" t="n">
-        <v>255</v>
+        <v>24</v>
       </c>
       <c r="U103" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V103" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W103" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X103" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y103" t="inlineStr">
@@ -21950,12 +21936,12 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
@@ -21965,7 +21951,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD103" t="inlineStr">
@@ -21980,7 +21966,7 @@
       </c>
       <c r="AF103" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG103" t="inlineStr">
@@ -22000,17 +21986,17 @@
       </c>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -22023,7 +22009,7 @@
       </c>
       <c r="AP103" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ103" t="inlineStr">
@@ -22031,62 +22017,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR103" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS103" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT103" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU103" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV103" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA103" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB103" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC103" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -22113,7 +22094,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -22157,106 +22138,31 @@
         </is>
       </c>
       <c r="N104" t="n">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="O104" t="n">
-        <v>167</v>
+        <v>255</v>
       </c>
       <c r="P104" t="n">
-        <v>167</v>
+        <v>255</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.07305847238561933</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U104" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V104" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W104" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X104" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y104" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD104" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE104" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF104" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG104" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI104" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM104" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN104" t="b">
-        <v>0</v>
       </c>
       <c r="AO104" t="inlineStr">
         <is>
@@ -22355,7 +22261,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -22390,7 +22296,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
@@ -22399,31 +22305,106 @@
         </is>
       </c>
       <c r="N105" t="n">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="O105" t="n">
-        <v>114</v>
+        <v>255</v>
       </c>
       <c r="P105" t="n">
-        <v>114</v>
-      </c>
-      <c r="R105" t="n">
-        <v>0.032661434713571</v>
-      </c>
-      <c r="S105" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>255</v>
       </c>
       <c r="U105" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
       </c>
       <c r="AO105" t="inlineStr">
         <is>
@@ -22557,7 +22538,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-06</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -22566,22 +22547,22 @@
         </is>
       </c>
       <c r="N106" t="n">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="O106" t="n">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="P106" t="n">
-        <v>114</v>
+        <v>167</v>
       </c>
       <c r="U106" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V106" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W106" t="inlineStr">
@@ -22591,7 +22572,7 @@
       </c>
       <c r="X106" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y106" t="inlineStr">
@@ -22656,7 +22637,7 @@
       </c>
       <c r="AK106" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM106" t="inlineStr">
@@ -22665,7 +22646,7 @@
         </is>
       </c>
       <c r="AN106" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO106" t="inlineStr">
         <is>
@@ -22764,7 +22745,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -22808,106 +22789,31 @@
         </is>
       </c>
       <c r="N107" t="n">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="O107" t="n">
-        <v>238</v>
+        <v>114</v>
       </c>
       <c r="P107" t="n">
-        <v>238</v>
+        <v>114</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.032661434713571</v>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U107" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V107" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W107" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X107" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y107" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD107" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE107" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF107" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG107" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM107" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN107" t="b">
-        <v>0</v>
       </c>
       <c r="AO107" t="inlineStr">
         <is>
@@ -23006,7 +22912,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -23041,7 +22947,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
@@ -23050,31 +22956,106 @@
         </is>
       </c>
       <c r="N108" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="O108" t="n">
-        <v>158</v>
+        <v>114</v>
       </c>
       <c r="P108" t="n">
-        <v>158</v>
-      </c>
-      <c r="R108" t="n">
-        <v>0.04526760249775628</v>
-      </c>
-      <c r="S108" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>114</v>
       </c>
       <c r="U108" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X108" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD108" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE108" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF108" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG108" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM108" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN108" t="b">
+        <v>1</v>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
@@ -23208,7 +23189,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -23217,22 +23198,22 @@
         </is>
       </c>
       <c r="N109" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="O109" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="P109" t="n">
-        <v>158</v>
+        <v>238</v>
       </c>
       <c r="U109" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V109" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W109" t="inlineStr">
@@ -23242,7 +23223,7 @@
       </c>
       <c r="X109" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y109" t="inlineStr">
@@ -23307,7 +23288,7 @@
       </c>
       <c r="AK109" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM109" t="inlineStr">
@@ -23316,7 +23297,7 @@
         </is>
       </c>
       <c r="AN109" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO109" t="inlineStr">
         <is>
@@ -23415,7 +23396,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -23459,106 +23440,31 @@
         </is>
       </c>
       <c r="N110" t="n">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="O110" t="n">
-        <v>266</v>
+        <v>158</v>
       </c>
       <c r="P110" t="n">
-        <v>266</v>
+        <v>158</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.04526760249775628</v>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U110" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V110" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W110" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X110" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y110" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD110" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE110" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF110" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG110" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI110" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN110" t="b">
-        <v>0</v>
       </c>
       <c r="AO110" t="inlineStr">
         <is>
@@ -23657,7 +23563,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -23692,7 +23598,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -23701,31 +23607,106 @@
         </is>
       </c>
       <c r="N111" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="O111" t="n">
-        <v>111</v>
+        <v>158</v>
       </c>
       <c r="P111" t="n">
-        <v>111</v>
-      </c>
-      <c r="R111" t="n">
-        <v>0.03180192327374018</v>
-      </c>
-      <c r="S111" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>158</v>
       </c>
       <c r="U111" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X111" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD111" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE111" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG111" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH111" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI111" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM111" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN111" t="b">
+        <v>1</v>
       </c>
       <c r="AO111" t="inlineStr">
         <is>
@@ -23859,7 +23840,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -23868,22 +23849,22 @@
         </is>
       </c>
       <c r="N112" t="n">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="O112" t="n">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="P112" t="n">
-        <v>111</v>
+        <v>266</v>
       </c>
       <c r="U112" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V112" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W112" t="inlineStr">
@@ -23893,7 +23874,7 @@
       </c>
       <c r="X112" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y112" t="inlineStr">
@@ -23958,7 +23939,7 @@
       </c>
       <c r="AK112" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM112" t="inlineStr">
@@ -23967,7 +23948,7 @@
         </is>
       </c>
       <c r="AN112" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO112" t="inlineStr">
         <is>
@@ -24066,7 +24047,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -24110,106 +24091,31 @@
         </is>
       </c>
       <c r="N113" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="O113" t="n">
-        <v>194</v>
+        <v>111</v>
       </c>
       <c r="P113" t="n">
-        <v>194</v>
+        <v>111</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.03180192327374018</v>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U113" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD113" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE113" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF113" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG113" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH113" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI113" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM113" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN113" t="b">
-        <v>0</v>
       </c>
       <c r="AO113" t="inlineStr">
         <is>
@@ -24308,17 +24214,17 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -24343,37 +24249,115 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="O114" t="n">
-        <v>21</v>
-      </c>
-      <c r="R114" t="n">
-        <v>0.3735499258814688</v>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>111</v>
+      </c>
+      <c r="P114" t="n">
+        <v>111</v>
       </c>
       <c r="U114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD114" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE114" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF114" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG114" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI114" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN114" t="b">
+        <v>1</v>
       </c>
       <c r="AO114" t="inlineStr">
         <is>
@@ -24382,65 +24366,70 @@
       </c>
       <c r="AP114" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ114" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR114" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS114" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU114" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA114" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB114" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC114" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24472,12 +24461,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -24502,38 +24491,41 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>21</v>
+        <v>194</v>
       </c>
       <c r="O115" t="n">
-        <v>21</v>
+        <v>194</v>
+      </c>
+      <c r="P115" t="n">
+        <v>194</v>
       </c>
       <c r="U115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W115" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X115" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y115" t="inlineStr">
@@ -24543,12 +24535,12 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
@@ -24558,7 +24550,7 @@
       </c>
       <c r="AC115" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD115" t="inlineStr">
@@ -24573,7 +24565,7 @@
       </c>
       <c r="AF115" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG115" t="inlineStr">
@@ -24593,21 +24585,21 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM115" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN115" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO115" t="inlineStr">
         <is>
@@ -24616,65 +24608,70 @@
       </c>
       <c r="AP115" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ115" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR115" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS115" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU115" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA115" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB115" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC115" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -24706,12 +24703,12 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -24745,13 +24742,13 @@
         </is>
       </c>
       <c r="N116" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O116" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="R116" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.3735499258814688</v>
       </c>
       <c r="S116" t="inlineStr">
         <is>
@@ -24760,7 +24757,7 @@
       </c>
       <c r="U116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -24780,12 +24777,12 @@
       </c>
       <c r="AQ116" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS116" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT116" t="n">
@@ -24793,47 +24790,47 @@
       </c>
       <c r="AU116" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA116" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB116" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC116" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -24865,12 +24862,12 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -24904,29 +24901,29 @@
         </is>
       </c>
       <c r="N117" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="O117" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="U117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W117" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X117" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y117" t="inlineStr">
@@ -24951,7 +24948,7 @@
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD117" t="inlineStr">
@@ -24986,17 +24983,17 @@
       </c>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM117" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN117" t="b">
@@ -25014,12 +25011,12 @@
       </c>
       <c r="AQ117" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS117" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT117" t="n">
@@ -25027,47 +25024,47 @@
       </c>
       <c r="AU117" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA117" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB117" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC117" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -25099,12 +25096,12 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -25129,7 +25126,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
@@ -25138,16 +25135,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="O118" t="n">
-        <v>63</v>
-      </c>
-      <c r="P118" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="R118" t="n">
-        <v>0.01804974023644713</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -25156,12 +25150,12 @@
       </c>
       <c r="U118" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO118" t="inlineStr">
@@ -25171,7 +25165,7 @@
       </c>
       <c r="AP118" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ118" t="inlineStr">
@@ -25179,62 +25173,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR118" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS118" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU118" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV118" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA118" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB118" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC118" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25266,12 +25255,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -25296,7 +25285,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -25305,32 +25294,29 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="O119" t="n">
-        <v>63</v>
-      </c>
-      <c r="P119" t="n">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V119" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W119" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X119" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y119" t="inlineStr">
@@ -25340,12 +25326,12 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
@@ -25355,7 +25341,7 @@
       </c>
       <c r="AC119" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD119" t="inlineStr">
@@ -25370,7 +25356,7 @@
       </c>
       <c r="AF119" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG119" t="inlineStr">
@@ -25390,17 +25376,17 @@
       </c>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -25413,7 +25399,7 @@
       </c>
       <c r="AP119" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ119" t="inlineStr">
@@ -25421,62 +25407,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR119" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS119" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU119" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV119" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA119" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB119" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC119" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -25503,7 +25484,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -25547,106 +25528,31 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>149</v>
+        <v>63</v>
       </c>
       <c r="O120" t="n">
-        <v>149</v>
+        <v>63</v>
       </c>
       <c r="P120" t="n">
-        <v>149</v>
+        <v>63</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.01804974023644713</v>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U120" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V120" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X120" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y120" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD120" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE120" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF120" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG120" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH120" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM120" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN120" t="b">
-        <v>0</v>
       </c>
       <c r="AO120" t="inlineStr">
         <is>
@@ -25745,7 +25651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -25780,7 +25686,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -25789,31 +25695,106 @@
         </is>
       </c>
       <c r="N121" t="n">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="O121" t="n">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="P121" t="n">
-        <v>119</v>
-      </c>
-      <c r="R121" t="n">
-        <v>0.03409395377995569</v>
-      </c>
-      <c r="S121" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>63</v>
       </c>
       <c r="U121" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD121" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE121" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF121" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG121" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM121" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN121" t="b">
+        <v>1</v>
       </c>
       <c r="AO121" t="inlineStr">
         <is>
@@ -25947,7 +25928,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -25956,22 +25937,22 @@
         </is>
       </c>
       <c r="N122" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="O122" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="P122" t="n">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="U122" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V122" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W122" t="inlineStr">
@@ -25981,7 +25962,7 @@
       </c>
       <c r="X122" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y122" t="inlineStr">
@@ -26046,7 +26027,7 @@
       </c>
       <c r="AK122" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM122" t="inlineStr">
@@ -26055,7 +26036,7 @@
         </is>
       </c>
       <c r="AN122" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO122" t="inlineStr">
         <is>
@@ -26154,7 +26135,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -26198,106 +26179,31 @@
         </is>
       </c>
       <c r="N123" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="O123" t="n">
-        <v>183</v>
+        <v>119</v>
       </c>
       <c r="P123" t="n">
-        <v>183</v>
+        <v>119</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.03409395377995569</v>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U123" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V123" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X123" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y123" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD123" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE123" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF123" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG123" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH123" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM123" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN123" t="b">
-        <v>0</v>
       </c>
       <c r="AO123" t="inlineStr">
         <is>
@@ -26396,7 +26302,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -26431,7 +26337,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -26440,31 +26346,106 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="O124" t="n">
-        <v>227</v>
+        <v>119</v>
       </c>
       <c r="P124" t="n">
-        <v>227</v>
-      </c>
-      <c r="R124" t="n">
-        <v>0.06503636561386504</v>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>119</v>
       </c>
       <c r="U124" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD124" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE124" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF124" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG124" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH124" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM124" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN124" t="b">
+        <v>1</v>
       </c>
       <c r="AO124" t="inlineStr">
         <is>
@@ -26598,7 +26579,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
@@ -26607,22 +26588,22 @@
         </is>
       </c>
       <c r="N125" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="O125" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="P125" t="n">
-        <v>227</v>
+        <v>183</v>
       </c>
       <c r="U125" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V125" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W125" t="inlineStr">
@@ -26632,7 +26613,7 @@
       </c>
       <c r="X125" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y125" t="inlineStr">
@@ -26697,7 +26678,7 @@
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM125" t="inlineStr">
@@ -26706,7 +26687,7 @@
         </is>
       </c>
       <c r="AN125" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
@@ -26805,7 +26786,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -26849,106 +26830,31 @@
         </is>
       </c>
       <c r="N126" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="O126" t="n">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="P126" t="n">
-        <v>241</v>
+        <v>227</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.06503636561386504</v>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U126" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V126" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X126" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y126" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z126" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB126" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD126" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE126" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF126" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG126" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH126" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI126" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM126" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN126" t="b">
-        <v>0</v>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
@@ -27047,7 +26953,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -27082,7 +26988,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
@@ -27091,31 +26997,106 @@
         </is>
       </c>
       <c r="N127" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="O127" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="P127" t="n">
-        <v>125</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.03581297665961732</v>
-      </c>
-      <c r="S127" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>227</v>
       </c>
       <c r="U127" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD127" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE127" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF127" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG127" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH127" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI127" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM127" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN127" t="b">
+        <v>1</v>
       </c>
       <c r="AO127" t="inlineStr">
         <is>
@@ -27249,7 +27230,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -27258,22 +27239,22 @@
         </is>
       </c>
       <c r="N128" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="O128" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="P128" t="n">
-        <v>125</v>
+        <v>241</v>
       </c>
       <c r="U128" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
@@ -27283,7 +27264,7 @@
       </c>
       <c r="X128" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y128" t="inlineStr">
@@ -27348,7 +27329,7 @@
       </c>
       <c r="AK128" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM128" t="inlineStr">
@@ -27357,7 +27338,7 @@
         </is>
       </c>
       <c r="AN128" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO128" t="inlineStr">
         <is>
@@ -27456,7 +27437,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -27500,106 +27481,31 @@
         </is>
       </c>
       <c r="N129" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="O129" t="n">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="P129" t="n">
-        <v>183</v>
+        <v>125</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.03581297665961732</v>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U129" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V129" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X129" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y129" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD129" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE129" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF129" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG129" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH129" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ129" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK129" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM129" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN129" t="b">
-        <v>0</v>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
@@ -27698,17 +27604,17 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -27733,37 +27639,115 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="O130" t="n">
-        <v>5</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0.08894045854320688</v>
-      </c>
-      <c r="S130" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>125</v>
+      </c>
+      <c r="P130" t="n">
+        <v>125</v>
       </c>
       <c r="U130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>monthly</t>
-        </is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD130" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE130" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF130" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG130" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH130" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM130" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN130" t="b">
+        <v>1</v>
       </c>
       <c r="AO130" t="inlineStr">
         <is>
@@ -27772,65 +27756,70 @@
       </c>
       <c r="AP130" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ130" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR130" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS130" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU130" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA130" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB130" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC130" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -27862,12 +27851,12 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -27892,38 +27881,41 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>183</v>
       </c>
       <c r="O131" t="n">
-        <v>5</v>
+        <v>183</v>
+      </c>
+      <c r="P131" t="n">
+        <v>183</v>
       </c>
       <c r="U131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y131" t="inlineStr">
@@ -27933,12 +27925,12 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
@@ -27948,7 +27940,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD131" t="inlineStr">
@@ -27963,7 +27955,7 @@
       </c>
       <c r="AF131" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG131" t="inlineStr">
@@ -27983,21 +27975,21 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN131" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
@@ -28006,65 +27998,70 @@
       </c>
       <c r="AP131" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>representative_series</t>
         </is>
       </c>
       <c r="AQ131" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR131" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
       <c r="AS131" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_141</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AT131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU131" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA131" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB131" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC131" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -28096,12 +28093,12 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -28135,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O132" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R132" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28150,7 +28147,7 @@
       </c>
       <c r="U132" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -28170,12 +28167,12 @@
       </c>
       <c r="AQ132" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS132" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT132" t="n">
@@ -28183,47 +28180,47 @@
       </c>
       <c r="AU132" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA132" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB132" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC132" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28255,12 +28252,12 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -28294,29 +28291,29 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="V133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="W133" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X133" t="inlineStr">
         <is>
-          <t>Hepatitt B, kronisk</t>
+          <t>Hepatitis B, chronic</t>
         </is>
       </c>
       <c r="Y133" t="inlineStr">
@@ -28341,7 +28338,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD133" t="inlineStr">
@@ -28376,17 +28373,17 @@
       </c>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
         </is>
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -28404,12 +28401,12 @@
       </c>
       <c r="AQ133" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS133" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_204_MONTHLY</t>
+          <t>SER_FI_THL_TTR_141</t>
         </is>
       </c>
       <c r="AT133" t="n">
@@ -28417,47 +28414,47 @@
       </c>
       <c r="AU133" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA133" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB133" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC133" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -28489,12 +28486,12 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -28528,16 +28525,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="O134" t="n">
-        <v>152</v>
-      </c>
-      <c r="P134" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="R134" t="n">
-        <v>0.04354857961809466</v>
+        <v>0.05306927477386519</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28546,12 +28540,12 @@
       </c>
       <c r="U134" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO134" t="inlineStr">
@@ -28561,7 +28555,7 @@
       </c>
       <c r="AP134" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ134" t="inlineStr">
@@ -28569,62 +28563,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR134" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS134" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU134" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV134" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA134" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB134" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC134" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28656,12 +28645,12 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -28695,32 +28684,29 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="O135" t="n">
-        <v>152</v>
-      </c>
-      <c r="P135" t="n">
-        <v>152</v>
+        <v>3</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="V135" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="W135" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X135" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitt B, kronisk</t>
         </is>
       </c>
       <c r="Y135" t="inlineStr">
@@ -28730,12 +28716,12 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
@@ -28745,7 +28731,7 @@
       </c>
       <c r="AC135" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD135" t="inlineStr">
@@ -28760,7 +28746,7 @@
       </c>
       <c r="AF135" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>conditional</t>
         </is>
       </c>
       <c r="AG135" t="inlineStr">
@@ -28780,17 +28766,17 @@
       </c>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
         </is>
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -28803,7 +28789,7 @@
       </c>
       <c r="AP135" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ135" t="inlineStr">
@@ -28811,62 +28797,57 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR135" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS135" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_NO_FHI_204_MONTHLY</t>
         </is>
       </c>
       <c r="AT135" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU135" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV135" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA135" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB135" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC135" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28893,7 +28874,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -28937,106 +28918,31 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="O136" t="n">
-        <v>231</v>
+        <v>152</v>
       </c>
       <c r="P136" t="n">
-        <v>231</v>
+        <v>152</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.04354857961809466</v>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V136" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W136" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X136" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y136" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC136" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD136" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE136" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF136" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG136" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH136" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ136" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK136" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM136" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN136" t="b">
-        <v>0</v>
       </c>
       <c r="AO136" t="inlineStr">
         <is>
@@ -29135,7 +29041,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -29170,7 +29076,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -29179,31 +29085,106 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="O137" t="n">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="P137" t="n">
-        <v>108</v>
-      </c>
-      <c r="R137" t="n">
-        <v>0.03094241183390936</v>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>152</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
           <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
       <c r="AA137" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD137" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE137" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF137" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG137" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH137" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM137" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN137" t="b">
+        <v>1</v>
       </c>
       <c r="AO137" t="inlineStr">
         <is>
@@ -29337,7 +29318,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
@@ -29346,22 +29327,22 @@
         </is>
       </c>
       <c r="N138" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="O138" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="P138" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="V138" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
         </is>
       </c>
       <c r="W138" t="inlineStr">
@@ -29371,7 +29352,7 @@
       </c>
       <c r="X138" t="inlineStr">
         <is>
-          <t>Hepatitis B, chronic, Confirmed</t>
+          <t>Hepatitis B, chronic, Probable</t>
         </is>
       </c>
       <c r="Y138" t="inlineStr">
@@ -29436,7 +29417,7 @@
       </c>
       <c r="AK138" t="inlineStr">
         <is>
-          <t>Confirmed chronic hepatitis B component.</t>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
         </is>
       </c>
       <c r="AM138" t="inlineStr">
@@ -29445,7 +29426,7 @@
         </is>
       </c>
       <c r="AN138" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO138" t="inlineStr">
         <is>
@@ -29544,7 +29525,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -29588,106 +29569,31 @@
         </is>
       </c>
       <c r="N139" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="O139" t="n">
-        <v>203</v>
+        <v>108</v>
       </c>
       <c r="P139" t="n">
-        <v>203</v>
+        <v>108</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.03094241183390936</v>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="V139" t="inlineStr">
-        <is>
-          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
-        </is>
-      </c>
-      <c r="W139" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X139" t="inlineStr">
-        <is>
-          <t>Hepatitis B, chronic, Probable</t>
-        </is>
-      </c>
-      <c r="Y139" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>notification</t>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD139" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE139" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF139" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="AG139" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH139" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI139" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
-        </is>
-      </c>
-      <c r="AM139" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN139" t="b">
-        <v>0</v>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
@@ -29758,6 +29664,490 @@
         </is>
       </c>
       <c r="BC139" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N140" t="n">
+        <v>108</v>
+      </c>
+      <c r="O140" t="n">
+        <v>108</v>
+      </c>
+      <c r="P140" t="n">
+        <v>108</v>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD140" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE140" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF140" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG140" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI140" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM140" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN140" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO140" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP140" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ140" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR140" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS140" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT140" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU140" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV140" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA140" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB140" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC140" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N141" t="n">
+        <v>203</v>
+      </c>
+      <c r="O141" t="n">
+        <v>203</v>
+      </c>
+      <c r="P141" t="n">
+        <v>203</v>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD141" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE141" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF141" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG141" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI141" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO141" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP141" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ141" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR141" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS141" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT141" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU141" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV141" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA141" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB141" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC141" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -29879,7 +30269,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -29889,7 +30279,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -29909,7 +30299,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13">
@@ -29941,7 +30331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9493</v>
+        <v>9597</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O132" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R132" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O133" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9597</v>
+        <v>9599</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -21352,13 +21352,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O100" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R100" t="n">
-        <v>0.3913380175901103</v>
+        <v>0.4091261092987516</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -21511,10 +21511,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O101" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -30331,7 +30331,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9599</v>
+        <v>9600</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -25135,13 +25135,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O118" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1592078243215956</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -25294,10 +25294,10 @@
         </is>
       </c>
       <c r="N119" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="O119" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="U119" t="inlineStr">
         <is>
@@ -28525,13 +28525,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R134" t="n">
-        <v>0.05306927477386519</v>
+        <v>0.08844879128977531</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28684,10 +28684,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O135" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -30148,6 +30148,657 @@
         </is>
       </c>
       <c r="BC141" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N142" t="n">
+        <v>111</v>
+      </c>
+      <c r="O142" t="n">
+        <v>111</v>
+      </c>
+      <c r="P142" t="n">
+        <v>111</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.03180192327374018</v>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP142" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ142" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR142" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS142" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT142" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU142" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV142" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA142" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB142" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC142" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N143" t="n">
+        <v>111</v>
+      </c>
+      <c r="O143" t="n">
+        <v>111</v>
+      </c>
+      <c r="P143" t="n">
+        <v>111</v>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD143" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE143" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF143" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG143" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI143" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN143" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP143" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ143" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT143" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU143" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV143" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA143" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB143" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC143" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N144" t="n">
+        <v>209</v>
+      </c>
+      <c r="O144" t="n">
+        <v>209</v>
+      </c>
+      <c r="P144" t="n">
+        <v>209</v>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD144" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE144" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF144" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG144" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI144" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.10</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM144" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP144" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ144" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR144" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS144" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT144" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU144" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV144" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA144" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB144" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC144" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -30186,7 +30837,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -30269,7 +30920,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10">
@@ -30279,7 +30930,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11">
@@ -30299,7 +30950,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13">
@@ -30331,7 +30982,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9600</v>
+        <v>9716</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O132" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R132" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.142304733669131</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O133" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9716</v>
+        <v>9717</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O132" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R132" t="n">
-        <v>0.142304733669131</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O133" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -28525,13 +28525,13 @@
         </is>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O134" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="R134" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.283036132127281</v>
       </c>
       <c r="S134" t="inlineStr">
         <is>
@@ -28684,10 +28684,10 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O135" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="U135" t="inlineStr">
         <is>
@@ -30982,7 +30982,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9717</v>
+        <v>9732</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O132" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2312451922123379</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O133" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -29170,7 +29170,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -30799,6 +30799,657 @@
         </is>
       </c>
       <c r="BC144" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N145" t="n">
+        <v>222</v>
+      </c>
+      <c r="O145" t="n">
+        <v>222</v>
+      </c>
+      <c r="P145" t="n">
+        <v>222</v>
+      </c>
+      <c r="R145" t="n">
+        <v>0.06360384654748036</v>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO145" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP145" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR145" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT145" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU145" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV145" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA145" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB145" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC145" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N146" t="n">
+        <v>222</v>
+      </c>
+      <c r="O146" t="n">
+        <v>222</v>
+      </c>
+      <c r="P146" t="n">
+        <v>222</v>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD146" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE146" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF146" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG146" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI146" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM146" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN146" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP146" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ146" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR146" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS146" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT146" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU146" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV146" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA146" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB146" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC146" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N147" t="n">
+        <v>199</v>
+      </c>
+      <c r="O147" t="n">
+        <v>199</v>
+      </c>
+      <c r="P147" t="n">
+        <v>199</v>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD147" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE147" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF147" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG147" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.28</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM147" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO147" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP147" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ147" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT147" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU147" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV147" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA147" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB147" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC147" t="inlineStr">
         <is>
           <t>api; api</t>
         </is>
@@ -30837,7 +31488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
@@ -30920,7 +31571,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -30930,7 +31581,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11">
@@ -30950,7 +31601,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -30982,7 +31633,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9732</v>
+        <v>9955</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -2188,7 +2188,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
@@ -2839,7 +2839,7 @@
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -8572,7 +8572,7 @@
       </c>
       <c r="AJ39" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK39" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
@@ -10399,7 +10399,7 @@
       </c>
       <c r="AJ48" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK48" t="inlineStr">
@@ -10641,7 +10641,7 @@
       </c>
       <c r="AJ49" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK49" t="inlineStr">
@@ -11050,7 +11050,7 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
@@ -11292,7 +11292,7 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -12352,7 +12352,7 @@
       </c>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK67" t="inlineStr">
@@ -14830,7 +14830,7 @@
       </c>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK69" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="AJ70" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK70" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
@@ -15723,7 +15723,7 @@
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
@@ -16132,7 +16132,7 @@
       </c>
       <c r="AJ75" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK75" t="inlineStr">
@@ -16374,7 +16374,7 @@
       </c>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK76" t="inlineStr">
@@ -17959,7 +17959,7 @@
       </c>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK84" t="inlineStr">
@@ -18201,7 +18201,7 @@
       </c>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK85" t="inlineStr">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -18852,7 +18852,7 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -19261,7 +19261,7 @@
       </c>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -19503,7 +19503,7 @@
       </c>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -20154,7 +20154,7 @@
       </c>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK94" t="inlineStr">
@@ -20563,7 +20563,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -22390,7 +22390,7 @@
       </c>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -22632,7 +22632,7 @@
       </c>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -23283,7 +23283,7 @@
       </c>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -23692,7 +23692,7 @@
       </c>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -23934,7 +23934,7 @@
       </c>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -24585,7 +24585,7 @@
       </c>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -25780,7 +25780,7 @@
       </c>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -26022,7 +26022,7 @@
       </c>
       <c r="AJ122" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK122" t="inlineStr">
@@ -26431,7 +26431,7 @@
       </c>
       <c r="AJ124" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK124" t="inlineStr">
@@ -26673,7 +26673,7 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
@@ -27082,7 +27082,7 @@
       </c>
       <c r="AJ127" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK127" t="inlineStr">
@@ -27324,7 +27324,7 @@
       </c>
       <c r="AJ128" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK128" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -27975,7 +27975,7 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -29170,7 +29170,7 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
@@ -29412,7 +29412,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -29821,7 +29821,7 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
@@ -30063,7 +30063,7 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
@@ -30472,7 +30472,7 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -30714,7 +30714,7 @@
       </c>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -31123,7 +31123,7 @@
       </c>
       <c r="AJ146" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK146" t="inlineStr">
@@ -31365,7 +31365,7 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">

--- a/diseases/d208/2026-2029.xlsx
+++ b/diseases/d208/2026-2029.xlsx
@@ -28132,13 +28132,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O132" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="R132" t="n">
-        <v>0.2312451922123379</v>
+        <v>0.284609467338262</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -28291,10 +28291,10 @@
         </is>
       </c>
       <c r="N133" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="O133" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="U133" t="inlineStr">
         <is>
@@ -31452,6 +31452,1443 @@
       <c r="BC147" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N148" t="n">
+        <v>95</v>
+      </c>
+      <c r="O148" t="n">
+        <v>95</v>
+      </c>
+      <c r="P148" t="n">
+        <v>95</v>
+      </c>
+      <c r="R148" t="n">
+        <v>0.02721786226130916</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO148" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP148" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ148" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR148" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS148" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT148" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU148" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV148" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA148" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB148" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC148" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N149" t="n">
+        <v>95</v>
+      </c>
+      <c r="O149" t="n">
+        <v>95</v>
+      </c>
+      <c r="P149" t="n">
+        <v>95</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Confirmed</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Confirmed chronic hepatitis B component.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO149" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP149" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR149" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT149" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU149" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV149" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA149" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB149" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC149" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N150" t="n">
+        <v>173</v>
+      </c>
+      <c r="O150" t="n">
+        <v>173</v>
+      </c>
+      <c r="P150" t="n">
+        <v>173</v>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_PROBABLE</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic, Probable</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD150" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE150" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF150" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG150" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH150" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>Probable chronic hepatitis B component retained as an independent source series.</t>
+        </is>
+      </c>
+      <c r="AM150" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO150" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP150" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ150" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr">
+        <is>
+          <t>SER_US_CHRONIC_HEPATITIS_B_CONFIRMED</t>
+        </is>
+      </c>
+      <c r="AT150" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU150" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV150" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA150" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB150" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC150" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N151" t="n">
+        <v>1</v>
+      </c>
+      <c r="O151" t="n">
+        <v>1</v>
+      </c>
+      <c r="R151" t="n">
+        <v>0.01778809170864137</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO151" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP151" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ151" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS151" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AT151" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU151" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV151" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA151" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB151" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC151" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N152" t="n">
+        <v>1</v>
+      </c>
+      <c r="O152" t="n">
+        <v>1</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Hepatitis B, chronic</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Course-qualified source series.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP152" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_141</t>
+        </is>
+      </c>
+      <c r="AT152" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU152" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV152" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA152" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB152" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC152" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" t="n">
+        <v>0</v>
+      </c>
+      <c r="R153" t="n">
+        <v>0</v>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO153" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP153" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ153" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT153" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU153" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA153" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB153" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC153" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>chronic-hepatitis-b</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>D208</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Chronic hepatitis B</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>慢性乙型肝炎</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="O154" t="n">
+        <v>0</v>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>Hepatitt B, kronisk</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD154" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE154" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF154" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG154" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH154" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS chronic category.</t>
+        </is>
+      </c>
+      <c r="AM154" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN154" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP154" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ154" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS154" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_204_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT154" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU154" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV154" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA154" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB154" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC154" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -31488,7 +32925,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -31571,7 +33008,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10">
@@ -31581,7 +33018,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11">
@@ -31601,7 +33038,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -31633,7 +33070,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>9955</v>
+        <v>10054</v>
       </c>
     </row>
     <row r="16">
